--- a/InputData/trans/RTMF/Recipient Transportation Mode Fractions.xlsx
+++ b/InputData/trans/RTMF/Recipient Transportation Mode Fractions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\trans\RTMF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\Vermont\VT-eps\InputData\trans\RTMF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879C9A3C-65AE-46B7-AAAF-3BEC51FB4A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E293AF-8834-4E41-899D-DEADBA852F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12870" yWindow="1470" windowWidth="22500" windowHeight="21135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="405" windowWidth="20115" windowHeight="14055" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -208,12 +208,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -234,9 +232,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -274,7 +272,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -380,7 +378,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -522,7 +520,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -600,30 +598,26 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-    </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
       <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
@@ -632,7 +626,6 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
       <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
@@ -641,7 +634,6 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
       <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
@@ -660,7 +652,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" customWidth="1"/>
@@ -669,7 +661,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -690,7 +682,7 @@
       <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -698,54 +690,52 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>0.33</v>
       </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0.33</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="6">
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
         <f>1-SUM(B2:G2)</f>
-        <v>0.33999999999999997</v>
+        <v>0.66999999999999993</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="6">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
         <f t="shared" ref="I3:I7" si="0">1-SUM(B3:G3)</f>
         <v>1</v>
       </c>
@@ -754,26 +744,25 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>0.25</v>
       </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="6">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
@@ -782,26 +771,25 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="6">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -810,26 +798,25 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="6">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -838,38 +825,28 @@
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="6">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -881,7 +858,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" customWidth="1"/>
@@ -890,7 +867,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -911,7 +888,7 @@
       <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -919,26 +896,25 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="6">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
         <f>1-SUM(B2:G2)</f>
         <v>1</v>
       </c>
@@ -947,26 +923,25 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="6">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
         <f t="shared" ref="I3:I7" si="0">1-SUM(B3:G3)</f>
         <v>1</v>
       </c>
@@ -975,26 +950,25 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="6">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1003,26 +977,25 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="6">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1031,26 +1004,25 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="6">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1059,38 +1031,28 @@
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="6">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
